--- a/01-projetos/01-data-project-foundations/data/input/absenteeism_data_46.xlsx
+++ b/01-projetos/01-data-project-foundations/data/input/absenteeism_data_46.xlsx
@@ -471,45 +471,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>39428</v>
+        <v>12482</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sophie Ribeiro</t>
+          <t>Maria Cecília Martins</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Engenharia</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>45087</v>
+        <v>45105</v>
       </c>
       <c r="G2" t="n">
-        <v>9887</v>
+        <v>9487.41</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>27071</v>
+        <v>38160</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nicole Caldeira</t>
+          <t>Lívia Barbosa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jurídico</t>
+          <t>Engenharia</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -518,80 +518,80 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45085</v>
+        <v>45106</v>
       </c>
       <c r="G3" t="n">
-        <v>4879.45</v>
+        <v>7649.18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>56760</v>
+        <v>9634</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bernardo da Mota</t>
+          <t>Vitor Hugo Jesus</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Engenharia</t>
+          <t>P&amp;D</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45085</v>
+        <v>45084</v>
       </c>
       <c r="G4" t="n">
-        <v>5659.13</v>
+        <v>9765.35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20888</v>
+        <v>15301</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Matheus da Cruz</t>
+          <t>Dra. Sofia Gonçalves</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vendas</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45082</v>
+        <v>45098</v>
       </c>
       <c r="G5" t="n">
-        <v>11536.96</v>
+        <v>5340.28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>34764</v>
+        <v>61786</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mirella Gonçalves</t>
+          <t>Vinicius Ferreira</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -601,162 +601,162 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45100</v>
+        <v>45094</v>
       </c>
       <c r="G6" t="n">
-        <v>12497.21</v>
+        <v>3187.39</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>77365</v>
+        <v>55565</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sra. Isabel da Cruz</t>
+          <t>Augusto da Cunha</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Engenharia</t>
+          <t>Operações</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Problemas pessoais</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>6</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45105</v>
+        <v>45078</v>
       </c>
       <c r="G7" t="n">
-        <v>12226.99</v>
+        <v>4215.94</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>26646</v>
+        <v>70894</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Maria Eduarda Cavalcanti</t>
+          <t>Renan Ribeiro</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Engenharia</t>
+          <t>Recursos Humanos</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45102</v>
+        <v>45089</v>
       </c>
       <c r="G8" t="n">
-        <v>12259.17</v>
+        <v>10511.26</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>36805</v>
+        <v>38653</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pietra Gomes</t>
+          <t>Dra. Maria Julia Farias</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>Operações</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Viagem de negócios</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45100</v>
+        <v>45087</v>
       </c>
       <c r="G9" t="n">
-        <v>3123.54</v>
+        <v>9540.940000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>52440</v>
+        <v>71366</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Augusto Caldeira</t>
+          <t>Sr. João Gabriel Pinto</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jurídico</t>
+          <t>Operações</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Consulta médica</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45100</v>
+        <v>45099</v>
       </c>
       <c r="G10" t="n">
-        <v>9019.76</v>
+        <v>9931.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>75372</v>
+        <v>29922</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Theo Melo</t>
+          <t>Bruno Martins</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atendimento ao Cliente</t>
+          <t>Recursos Humanos</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Problemas pessoais</t>
+          <t>Doença</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45089</v>
+        <v>45087</v>
       </c>
       <c r="G11" t="n">
-        <v>4385.34</v>
+        <v>7294.01</v>
       </c>
     </row>
   </sheetData>
